--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java_Developer_Roadmap\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java_Developer_Roadmap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3563FAEE-F576-4467-A1ED-B9E5C7DF2F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088C8110-F6FC-40A9-A126-26F344062097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="296">
   <si>
     <t>Level</t>
   </si>
@@ -912,6 +912,9 @@
   </si>
   <si>
     <t>Java Developer</t>
+  </si>
+  <si>
+    <t>Completed</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1320,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,7 +1337,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,7 +1354,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1368,7 +1371,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1385,7 +1388,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1402,7 +1405,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1419,7 +1422,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1436,7 +1439,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>36</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1452,9 +1455,7 @@
       <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1469,9 +1470,7 @@
       <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1486,9 +1485,7 @@
       <c r="D12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1503,9 +1500,7 @@
       <c r="D13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1520,9 +1515,7 @@
       <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -1537,9 +1530,7 @@
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -1554,9 +1545,7 @@
       <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -1571,9 +1560,7 @@
       <c r="D17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -1588,9 +1575,7 @@
       <c r="D18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
@@ -1605,9 +1590,7 @@
       <c r="D19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1622,9 +1605,7 @@
       <c r="D20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -1639,9 +1620,7 @@
       <c r="D21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1656,9 +1635,7 @@
       <c r="D22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -1673,9 +1650,7 @@
       <c r="D23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -1690,9 +1665,7 @@
       <c r="D24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1707,9 +1680,7 @@
       <c r="D25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
@@ -1724,9 +1695,7 @@
       <c r="D26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -1741,9 +1710,7 @@
       <c r="D27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -1758,9 +1725,7 @@
       <c r="D28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -1775,9 +1740,7 @@
       <c r="D29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -1792,9 +1755,7 @@
       <c r="D30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
@@ -1809,9 +1770,7 @@
       <c r="D31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -1826,9 +1785,7 @@
       <c r="D32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
@@ -1843,9 +1800,7 @@
       <c r="D33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
@@ -1860,9 +1815,7 @@
       <c r="D34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -1877,9 +1830,7 @@
       <c r="D35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -1894,9 +1845,7 @@
       <c r="D36" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -1911,9 +1860,7 @@
       <c r="D37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -1928,9 +1875,7 @@
       <c r="D38" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
@@ -1945,9 +1890,7 @@
       <c r="D39" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -1962,9 +1905,7 @@
       <c r="D40" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
@@ -1979,9 +1920,7 @@
       <c r="D41" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
@@ -1996,9 +1935,7 @@
       <c r="D42" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -2013,9 +1950,7 @@
       <c r="D43" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -2030,9 +1965,7 @@
       <c r="D44" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
@@ -2047,9 +1980,7 @@
       <c r="D45" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -2064,9 +1995,7 @@
       <c r="D46" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -2081,9 +2010,7 @@
       <c r="D47" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -2098,9 +2025,7 @@
       <c r="D48" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -2115,9 +2040,7 @@
       <c r="D49" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
@@ -2132,9 +2055,7 @@
       <c r="D50" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -2149,9 +2070,7 @@
       <c r="D51" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
@@ -2166,9 +2085,7 @@
       <c r="D52" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
@@ -2183,9 +2100,7 @@
       <c r="D53" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
@@ -2200,9 +2115,7 @@
       <c r="D54" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
@@ -2217,9 +2130,7 @@
       <c r="D55" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
@@ -2234,9 +2145,7 @@
       <c r="D56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
@@ -2251,9 +2160,7 @@
       <c r="D57" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
@@ -2268,9 +2175,7 @@
       <c r="D58" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
@@ -2285,9 +2190,7 @@
       <c r="D59" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
@@ -2302,9 +2205,7 @@
       <c r="D60" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
@@ -2319,9 +2220,7 @@
       <c r="D61" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
@@ -2336,9 +2235,7 @@
       <c r="D62" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E62" s="3"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
@@ -2353,9 +2250,7 @@
       <c r="D63" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
@@ -2370,9 +2265,7 @@
       <c r="D64" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
@@ -2387,9 +2280,7 @@
       <c r="D65" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
@@ -2404,9 +2295,7 @@
       <c r="D66" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
@@ -2421,9 +2310,7 @@
       <c r="D67" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
@@ -2438,9 +2325,7 @@
       <c r="D68" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
@@ -2455,9 +2340,7 @@
       <c r="D69" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E69" s="3"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
@@ -2472,9 +2355,7 @@
       <c r="D70" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
@@ -2489,9 +2370,7 @@
       <c r="D71" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E71" s="3"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
@@ -2506,9 +2385,7 @@
       <c r="D72" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E72" s="3"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
@@ -2523,9 +2400,7 @@
       <c r="D73" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E73" s="3"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
@@ -2540,9 +2415,7 @@
       <c r="D74" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E74" s="3"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
@@ -2557,9 +2430,7 @@
       <c r="D75" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E75" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E75" s="3"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
@@ -2574,9 +2445,7 @@
       <c r="D76" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
@@ -2591,9 +2460,7 @@
       <c r="D77" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
@@ -2608,9 +2475,7 @@
       <c r="D78" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
@@ -2625,9 +2490,7 @@
       <c r="D79" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
@@ -2642,9 +2505,7 @@
       <c r="D80" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
@@ -2659,9 +2520,7 @@
       <c r="D81" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
@@ -2676,9 +2535,7 @@
       <c r="D82" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
@@ -2693,9 +2550,7 @@
       <c r="D83" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
@@ -2710,9 +2565,7 @@
       <c r="D84" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
@@ -2727,9 +2580,7 @@
       <c r="D85" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E85" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
@@ -2744,9 +2595,7 @@
       <c r="D86" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
@@ -2761,9 +2610,7 @@
       <c r="D87" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
@@ -2778,9 +2625,7 @@
       <c r="D88" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
@@ -2795,9 +2640,7 @@
       <c r="D89" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
@@ -2812,9 +2655,7 @@
       <c r="D90" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
@@ -2829,9 +2670,7 @@
       <c r="D91" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
@@ -2846,9 +2685,7 @@
       <c r="D92" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
@@ -2863,9 +2700,7 @@
       <c r="D93" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
@@ -2880,9 +2715,7 @@
       <c r="D94" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
@@ -2897,9 +2730,7 @@
       <c r="D95" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
@@ -2914,9 +2745,7 @@
       <c r="D96" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
@@ -2931,9 +2760,7 @@
       <c r="D97" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
@@ -2948,9 +2775,7 @@
       <c r="D98" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E98" s="3"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
@@ -2965,9 +2790,7 @@
       <c r="D99" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
@@ -2982,9 +2805,7 @@
       <c r="D100" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
@@ -2999,9 +2820,7 @@
       <c r="D101" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
@@ -3016,9 +2835,7 @@
       <c r="D102" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
@@ -3033,9 +2850,7 @@
       <c r="D103" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
@@ -3050,9 +2865,7 @@
       <c r="D104" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E104" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
@@ -3067,9 +2880,7 @@
       <c r="D105" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E105" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
@@ -3084,9 +2895,7 @@
       <c r="D106" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
@@ -3101,9 +2910,7 @@
       <c r="D107" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
@@ -3118,9 +2925,7 @@
       <c r="D108" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
@@ -3135,9 +2940,7 @@
       <c r="D109" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E109" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
@@ -3152,9 +2955,7 @@
       <c r="D110" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E110" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
@@ -3169,9 +2970,7 @@
       <c r="D111" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
@@ -3186,9 +2985,7 @@
       <c r="D112" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E112" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
@@ -3203,9 +3000,7 @@
       <c r="D113" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E113" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E113" s="3"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
@@ -3220,9 +3015,7 @@
       <c r="D114" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E114" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E114" s="3"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
@@ -3237,9 +3030,7 @@
       <c r="D115" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E115" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E115" s="3"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
@@ -3254,9 +3045,7 @@
       <c r="D116" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E116" s="3"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
@@ -3271,9 +3060,7 @@
       <c r="D117" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E117" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E117" s="3"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
@@ -3288,9 +3075,7 @@
       <c r="D118" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E118" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E118" s="3"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
@@ -3305,9 +3090,7 @@
       <c r="D119" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E119" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E119" s="3"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
@@ -3322,9 +3105,7 @@
       <c r="D120" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E120" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E120" s="3"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
@@ -3339,9 +3120,7 @@
       <c r="D121" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E121" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E121" s="3"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
@@ -3356,9 +3135,7 @@
       <c r="D122" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E122" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
@@ -3373,9 +3150,7 @@
       <c r="D123" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E123" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
@@ -3390,9 +3165,7 @@
       <c r="D124" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E124" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E124" s="3"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
@@ -3407,9 +3180,7 @@
       <c r="D125" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E125" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E125" s="3"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
@@ -3424,9 +3195,7 @@
       <c r="D126" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E126" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E126" s="3"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
@@ -3441,9 +3210,7 @@
       <c r="D127" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E127" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
@@ -3458,9 +3225,7 @@
       <c r="D128" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E128" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E128" s="3"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
@@ -3475,9 +3240,7 @@
       <c r="D129" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E129" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E129" s="3"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
@@ -3492,9 +3255,7 @@
       <c r="D130" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E130" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E130" s="3"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
@@ -3509,9 +3270,7 @@
       <c r="D131" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E131" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E131" s="3"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
@@ -3526,9 +3285,7 @@
       <c r="D132" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E132" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E132" s="3"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
@@ -3543,9 +3300,7 @@
       <c r="D133" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E133" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E133" s="3"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
@@ -3560,9 +3315,7 @@
       <c r="D134" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E134" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E134" s="3"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
@@ -3577,9 +3330,7 @@
       <c r="D135" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E135" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E135" s="3"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
@@ -3594,9 +3345,7 @@
       <c r="D136" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E136" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E136" s="3"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
@@ -3611,9 +3360,7 @@
       <c r="D137" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E137" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E137" s="3"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
@@ -3628,9 +3375,7 @@
       <c r="D138" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E138" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E138" s="3"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
@@ -3645,9 +3390,7 @@
       <c r="D139" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E139" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E139" s="3"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
@@ -3662,9 +3405,7 @@
       <c r="D140" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E140" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E140" s="3"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
@@ -3679,9 +3420,7 @@
       <c r="D141" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E141" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E141" s="3"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
@@ -3696,9 +3435,7 @@
       <c r="D142" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E142" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E142" s="3"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
@@ -3713,9 +3450,7 @@
       <c r="D143" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E143" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E143" s="3"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
@@ -3730,9 +3465,7 @@
       <c r="D144" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E144" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E144" s="3"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
@@ -3747,9 +3480,7 @@
       <c r="D145" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E145" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E145" s="3"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
@@ -3764,9 +3495,7 @@
       <c r="D146" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E146" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E146" s="3"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
@@ -3781,9 +3510,7 @@
       <c r="D147" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E147" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
@@ -3798,9 +3525,7 @@
       <c r="D148" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E148" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E148" s="3"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
@@ -3815,9 +3540,7 @@
       <c r="D149" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E149" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
@@ -3832,9 +3555,7 @@
       <c r="D150" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E150" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E150" s="3"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
@@ -3849,9 +3570,7 @@
       <c r="D151" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E151" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
@@ -3866,9 +3585,7 @@
       <c r="D152" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E152" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E152" s="3"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
@@ -3883,9 +3600,7 @@
       <c r="D153" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E153" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E153" s="3"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
@@ -3900,9 +3615,7 @@
       <c r="D154" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E154" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E154" s="3"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
@@ -3917,9 +3630,7 @@
       <c r="D155" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E155" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E155" s="3"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
@@ -3934,9 +3645,7 @@
       <c r="D156" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E156" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E156" s="3"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
@@ -3951,9 +3660,7 @@
       <c r="D157" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E157" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E157" s="3"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
@@ -3968,9 +3675,7 @@
       <c r="D158" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E158" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E158" s="3"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
@@ -3985,9 +3690,7 @@
       <c r="D159" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E159" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E159" s="3"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
@@ -4002,9 +3705,7 @@
       <c r="D160" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E160" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E160" s="3"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
@@ -4019,9 +3720,7 @@
       <c r="D161" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E161" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E161" s="3"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
@@ -4036,9 +3735,7 @@
       <c r="D162" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E162" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E162" s="3"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
@@ -4053,9 +3750,7 @@
       <c r="D163" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E163" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E163" s="3"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
@@ -4070,9 +3765,7 @@
       <c r="D164" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E164" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E164" s="3"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
@@ -4087,9 +3780,7 @@
       <c r="D165" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E165" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E165" s="3"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
@@ -4104,9 +3795,7 @@
       <c r="D166" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E166" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E166" s="3"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
@@ -4121,9 +3810,7 @@
       <c r="D167" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E167" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E167" s="3"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
@@ -4138,9 +3825,7 @@
       <c r="D168" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E168" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E168" s="3"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
@@ -4155,9 +3840,7 @@
       <c r="D169" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E169" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E169" s="3"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
@@ -4172,9 +3855,7 @@
       <c r="D170" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E170" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E170" s="3"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
@@ -4189,9 +3870,7 @@
       <c r="D171" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E171" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E171" s="3"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
@@ -4206,9 +3885,7 @@
       <c r="D172" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E172" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E172" s="3"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
@@ -4223,9 +3900,7 @@
       <c r="D173" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E173" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E173" s="3"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
@@ -4240,9 +3915,7 @@
       <c r="D174" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E174" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E174" s="3"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
@@ -4257,9 +3930,7 @@
       <c r="D175" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E175" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E175" s="3"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
@@ -4274,9 +3945,7 @@
       <c r="D176" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E176" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E176" s="3"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
@@ -4291,9 +3960,7 @@
       <c r="D177" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E177" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E177" s="3"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
@@ -4308,9 +3975,7 @@
       <c r="D178" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E178" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E178" s="3"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
@@ -4325,9 +3990,7 @@
       <c r="D179" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E179" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E179" s="3"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
@@ -4342,9 +4005,7 @@
       <c r="D180" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E180" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E180" s="3"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
@@ -4359,9 +4020,7 @@
       <c r="D181" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E181" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E181" s="3"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
@@ -4376,9 +4035,7 @@
       <c r="D182" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E182" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E182" s="3"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
@@ -4393,9 +4050,7 @@
       <c r="D183" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E183" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E183" s="3"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
@@ -4410,9 +4065,7 @@
       <c r="D184" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E184" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E184" s="3"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
@@ -4427,9 +4080,7 @@
       <c r="D185" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E185" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E185" s="3"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
@@ -4444,9 +4095,7 @@
       <c r="D186" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E186" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E186" s="3"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
@@ -4461,9 +4110,7 @@
       <c r="D187" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E187" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E187" s="3"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
@@ -4478,9 +4125,7 @@
       <c r="D188" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E188" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E188" s="3"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
@@ -4495,9 +4140,7 @@
       <c r="D189" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E189" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E189" s="3"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
@@ -4512,9 +4155,7 @@
       <c r="D190" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E190" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E190" s="3"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
@@ -4529,9 +4170,7 @@
       <c r="D191" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E191" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E191" s="3"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
@@ -4546,9 +4185,7 @@
       <c r="D192" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E192" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E192" s="3"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
@@ -4563,9 +4200,7 @@
       <c r="D193" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E193" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E193" s="3"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
@@ -4580,9 +4215,7 @@
       <c r="D194" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E194" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E194" s="3"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
@@ -4597,9 +4230,7 @@
       <c r="D195" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E195" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E195" s="3"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
@@ -4614,9 +4245,7 @@
       <c r="D196" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E196" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E196" s="3"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
@@ -4631,9 +4260,7 @@
       <c r="D197" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E197" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E197" s="3"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
@@ -4648,9 +4275,7 @@
       <c r="D198" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E198" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E198" s="3"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
@@ -4665,9 +4290,7 @@
       <c r="D199" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E199" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E199" s="3"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
@@ -4682,9 +4305,7 @@
       <c r="D200" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E200" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E200" s="3"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
@@ -4699,9 +4320,7 @@
       <c r="D201" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E201" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E201" s="3"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
@@ -4716,9 +4335,7 @@
       <c r="D202" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E202" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E202" s="3"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
@@ -4733,9 +4350,7 @@
       <c r="D203" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E203" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E203" s="3"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
@@ -4750,9 +4365,7 @@
       <c r="D204" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E204" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E204" s="3"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
@@ -4767,9 +4380,7 @@
       <c r="D205" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E205" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E205" s="3"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
@@ -4784,9 +4395,7 @@
       <c r="D206" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E206" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E206" s="3"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
@@ -4801,9 +4410,7 @@
       <c r="D207" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E207" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E207" s="3"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
@@ -4818,9 +4425,7 @@
       <c r="D208" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E208" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E208" s="3"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
@@ -4835,9 +4440,7 @@
       <c r="D209" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E209" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E209" s="3"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
@@ -4852,9 +4455,7 @@
       <c r="D210" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E210" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E210" s="3"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
@@ -4869,9 +4470,7 @@
       <c r="D211" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E211" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E211" s="3"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
@@ -4886,9 +4485,7 @@
       <c r="D212" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E212" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E212" s="3"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
@@ -4903,9 +4500,7 @@
       <c r="D213" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E213" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E213" s="3"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
@@ -4920,9 +4515,7 @@
       <c r="D214" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E214" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E214" s="3"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
@@ -4937,9 +4530,7 @@
       <c r="D215" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E215" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E215" s="3"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
@@ -4954,9 +4545,7 @@
       <c r="D216" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E216" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E216" s="3"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
@@ -4971,9 +4560,7 @@
       <c r="D217" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E217" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E217" s="3"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
@@ -4988,9 +4575,7 @@
       <c r="D218" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E218" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E218" s="3"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
@@ -5005,9 +4590,7 @@
       <c r="D219" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E219" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E219" s="3"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
@@ -5022,9 +4605,7 @@
       <c r="D220" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E220" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="E220" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E220" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java_Developer_Roadmap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088C8110-F6FC-40A9-A126-26F344062097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBDED73-4AA5-4653-8FBE-8A1AE45061D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="296">
   <si>
     <t>Level</t>
   </si>
@@ -1455,7 +1455,9 @@
       <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1470,7 +1472,9 @@
       <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1485,7 +1489,9 @@
       <c r="D12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1500,7 +1506,9 @@
       <c r="D13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">

--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DB23D5-7F64-4588-837A-A60304EF332D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Roadmap" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Topics &amp; Subtopics" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Progress" state="visible" r:id="rId6"/>
+    <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
+    <sheet name="Topics &amp; Subtopics" sheetId="2" r:id="rId2"/>
+    <sheet name="Progress" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Topics &amp; Subtopics'!$A$1:$C$29</definedName>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="296">
   <si>
     <t>Level</t>
   </si>
@@ -912,19 +913,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1270,9 +1271,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E220"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1587,7 +1588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -1600,9 +1601,11 @@
       <c r="D19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1615,9 +1618,11 @@
       <c r="D20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -1630,9 +1635,11 @@
       <c r="D21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
@@ -1645,7 +1652,9 @@
       <c r="D22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
@@ -1857,7 +1866,7 @@
       </c>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>26</v>
       </c>
@@ -1872,7 +1881,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>26</v>
       </c>
@@ -1887,7 +1896,7 @@
       </c>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>26</v>
       </c>
@@ -1902,7 +1911,7 @@
       </c>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>26</v>
       </c>
@@ -1917,7 +1926,7 @@
       </c>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>26</v>
       </c>
@@ -1932,7 +1941,7 @@
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
@@ -1947,7 +1956,7 @@
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>26</v>
       </c>
@@ -1962,7 +1971,7 @@
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>26</v>
       </c>
@@ -1977,7 +1986,7 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>26</v>
       </c>
@@ -1992,7 +2001,7 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>26</v>
       </c>
@@ -2007,7 +2016,7 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>26</v>
       </c>
@@ -2022,7 +2031,7 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>26</v>
       </c>
@@ -2037,7 +2046,7 @@
       </c>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
@@ -2052,7 +2061,7 @@
       </c>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>61</v>
       </c>
@@ -2067,7 +2076,7 @@
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>61</v>
       </c>
@@ -2082,7 +2091,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>61</v>
       </c>
@@ -2097,7 +2106,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>61</v>
       </c>
@@ -2112,7 +2121,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>61</v>
       </c>
@@ -2127,7 +2136,7 @@
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>61</v>
       </c>
@@ -2142,7 +2151,7 @@
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
@@ -2157,7 +2166,7 @@
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
@@ -2172,7 +2181,7 @@
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>61</v>
       </c>
@@ -2187,7 +2196,7 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -2202,7 +2211,7 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>61</v>
       </c>
@@ -2217,7 +2226,7 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
@@ -2232,7 +2241,7 @@
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>61</v>
       </c>
@@ -2247,7 +2256,7 @@
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
@@ -2262,7 +2271,7 @@
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>61</v>
       </c>
@@ -2277,7 +2286,7 @@
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>61</v>
       </c>
@@ -2292,7 +2301,7 @@
       </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -2307,7 +2316,7 @@
       </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>61</v>
       </c>
@@ -2322,7 +2331,7 @@
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>61</v>
       </c>
@@ -2337,7 +2346,7 @@
       </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>61</v>
       </c>
@@ -2352,7 +2361,7 @@
       </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>61</v>
       </c>
@@ -2367,7 +2376,7 @@
       </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>61</v>
       </c>
@@ -2382,7 +2391,7 @@
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>61</v>
       </c>
@@ -2397,7 +2406,7 @@
       </c>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>61</v>
       </c>
@@ -2412,7 +2421,7 @@
       </c>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>61</v>
       </c>
@@ -2427,7 +2436,7 @@
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>61</v>
       </c>
@@ -2442,7 +2451,7 @@
       </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>61</v>
       </c>
@@ -2457,7 +2466,7 @@
       </c>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>61</v>
       </c>
@@ -2472,7 +2481,7 @@
       </c>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -2487,7 +2496,7 @@
       </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>61</v>
       </c>
@@ -2502,7 +2511,7 @@
       </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>61</v>
       </c>
@@ -2517,7 +2526,7 @@
       </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>61</v>
       </c>
@@ -2532,7 +2541,7 @@
       </c>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>61</v>
       </c>
@@ -2547,7 +2556,7 @@
       </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>61</v>
       </c>
@@ -2562,7 +2571,7 @@
       </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>61</v>
       </c>
@@ -2577,7 +2586,7 @@
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
@@ -2592,7 +2601,7 @@
       </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>61</v>
       </c>
@@ -2607,7 +2616,7 @@
       </c>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>61</v>
       </c>
@@ -2622,7 +2631,7 @@
       </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
@@ -2637,7 +2646,7 @@
       </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>61</v>
       </c>
@@ -2652,7 +2661,7 @@
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>61</v>
       </c>
@@ -2667,7 +2676,7 @@
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>61</v>
       </c>
@@ -2682,7 +2691,7 @@
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>61</v>
       </c>
@@ -2697,7 +2706,7 @@
       </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>61</v>
       </c>
@@ -2712,7 +2721,7 @@
       </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>61</v>
       </c>
@@ -2727,7 +2736,7 @@
       </c>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>61</v>
       </c>
@@ -2742,7 +2751,7 @@
       </c>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>61</v>
       </c>
@@ -2757,7 +2766,7 @@
       </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>61</v>
       </c>
@@ -2772,7 +2781,7 @@
       </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>61</v>
       </c>
@@ -2787,7 +2796,7 @@
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>61</v>
       </c>
@@ -2802,7 +2811,7 @@
       </c>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>61</v>
       </c>
@@ -2817,7 +2826,7 @@
       </c>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>120</v>
       </c>
@@ -2832,7 +2841,7 @@
       </c>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>120</v>
       </c>
@@ -2847,7 +2856,7 @@
       </c>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>120</v>
       </c>
@@ -2862,7 +2871,7 @@
       </c>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
@@ -2877,7 +2886,7 @@
       </c>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>120</v>
       </c>
@@ -2892,7 +2901,7 @@
       </c>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>120</v>
       </c>
@@ -2907,7 +2916,7 @@
       </c>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>120</v>
       </c>
@@ -2922,7 +2931,7 @@
       </c>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>120</v>
       </c>
@@ -2937,7 +2946,7 @@
       </c>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>120</v>
       </c>
@@ -2952,7 +2961,7 @@
       </c>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>120</v>
       </c>
@@ -2967,7 +2976,7 @@
       </c>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>120</v>
       </c>
@@ -2982,7 +2991,7 @@
       </c>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>120</v>
       </c>
@@ -2997,7 +3006,7 @@
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>120</v>
       </c>
@@ -3012,7 +3021,7 @@
       </c>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>120</v>
       </c>
@@ -3027,7 +3036,7 @@
       </c>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>120</v>
       </c>
@@ -3042,7 +3051,7 @@
       </c>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>120</v>
       </c>
@@ -3057,7 +3066,7 @@
       </c>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>120</v>
       </c>
@@ -3072,7 +3081,7 @@
       </c>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>120</v>
       </c>
@@ -3087,7 +3096,7 @@
       </c>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>120</v>
       </c>
@@ -3102,7 +3111,7 @@
       </c>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>120</v>
       </c>
@@ -3117,7 +3126,7 @@
       </c>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>120</v>
       </c>
@@ -3132,7 +3141,7 @@
       </c>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
@@ -3147,7 +3156,7 @@
       </c>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>120</v>
       </c>
@@ -3162,7 +3171,7 @@
       </c>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>120</v>
       </c>
@@ -3177,7 +3186,7 @@
       </c>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -3192,7 +3201,7 @@
       </c>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
@@ -3207,7 +3216,7 @@
       </c>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>120</v>
       </c>
@@ -3222,7 +3231,7 @@
       </c>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>120</v>
       </c>
@@ -3237,7 +3246,7 @@
       </c>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>120</v>
       </c>
@@ -3252,7 +3261,7 @@
       </c>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>120</v>
       </c>
@@ -3267,7 +3276,7 @@
       </c>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>120</v>
       </c>
@@ -3282,7 +3291,7 @@
       </c>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>120</v>
       </c>
@@ -3297,7 +3306,7 @@
       </c>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
@@ -3312,7 +3321,7 @@
       </c>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>158</v>
       </c>
@@ -3327,7 +3336,7 @@
       </c>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>158</v>
       </c>
@@ -3342,7 +3351,7 @@
       </c>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>158</v>
       </c>
@@ -3357,7 +3366,7 @@
       </c>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>158</v>
       </c>
@@ -3372,7 +3381,7 @@
       </c>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>158</v>
       </c>
@@ -3387,7 +3396,7 @@
       </c>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>158</v>
       </c>
@@ -3402,7 +3411,7 @@
       </c>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>158</v>
       </c>
@@ -3417,7 +3426,7 @@
       </c>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>158</v>
       </c>
@@ -3432,7 +3441,7 @@
       </c>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>158</v>
       </c>
@@ -3447,7 +3456,7 @@
       </c>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>158</v>
       </c>
@@ -3462,7 +3471,7 @@
       </c>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>158</v>
       </c>
@@ -3477,7 +3486,7 @@
       </c>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>158</v>
       </c>
@@ -3492,7 +3501,7 @@
       </c>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>158</v>
       </c>
@@ -3507,7 +3516,7 @@
       </c>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>158</v>
       </c>
@@ -3522,7 +3531,7 @@
       </c>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
@@ -3537,7 +3546,7 @@
       </c>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>158</v>
       </c>
@@ -3552,7 +3561,7 @@
       </c>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>158</v>
       </c>
@@ -3567,7 +3576,7 @@
       </c>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>158</v>
       </c>
@@ -3582,7 +3591,7 @@
       </c>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>158</v>
       </c>
@@ -3597,7 +3606,7 @@
       </c>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>158</v>
       </c>
@@ -3612,7 +3621,7 @@
       </c>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>158</v>
       </c>
@@ -3627,7 +3636,7 @@
       </c>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>158</v>
       </c>
@@ -3642,7 +3651,7 @@
       </c>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
@@ -3657,7 +3666,7 @@
       </c>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>158</v>
       </c>
@@ -3672,7 +3681,7 @@
       </c>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>158</v>
       </c>
@@ -3687,7 +3696,7 @@
       </c>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>158</v>
       </c>
@@ -3702,7 +3711,7 @@
       </c>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>158</v>
       </c>
@@ -3717,7 +3726,7 @@
       </c>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>158</v>
       </c>
@@ -3732,7 +3741,7 @@
       </c>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>158</v>
       </c>
@@ -3747,7 +3756,7 @@
       </c>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>158</v>
       </c>
@@ -3762,7 +3771,7 @@
       </c>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>158</v>
       </c>
@@ -3777,7 +3786,7 @@
       </c>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>158</v>
       </c>
@@ -3792,7 +3801,7 @@
       </c>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>158</v>
       </c>
@@ -3807,7 +3816,7 @@
       </c>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -3822,7 +3831,7 @@
       </c>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>158</v>
       </c>
@@ -3837,7 +3846,7 @@
       </c>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>158</v>
       </c>
@@ -3852,7 +3861,7 @@
       </c>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>158</v>
       </c>
@@ -3867,7 +3876,7 @@
       </c>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>158</v>
       </c>
@@ -3882,7 +3891,7 @@
       </c>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>158</v>
       </c>
@@ -3897,7 +3906,7 @@
       </c>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>158</v>
       </c>
@@ -3912,7 +3921,7 @@
       </c>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>158</v>
       </c>
@@ -3927,7 +3936,7 @@
       </c>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>158</v>
       </c>
@@ -3942,7 +3951,7 @@
       </c>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>158</v>
       </c>
@@ -3957,7 +3966,7 @@
       </c>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>158</v>
       </c>
@@ -3972,7 +3981,7 @@
       </c>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>158</v>
       </c>
@@ -3987,7 +3996,7 @@
       </c>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>158</v>
       </c>
@@ -4002,7 +4011,7 @@
       </c>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>158</v>
       </c>
@@ -4017,7 +4026,7 @@
       </c>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>158</v>
       </c>
@@ -4032,7 +4041,7 @@
       </c>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>158</v>
       </c>
@@ -4047,7 +4056,7 @@
       </c>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>158</v>
       </c>
@@ -4062,7 +4071,7 @@
       </c>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>158</v>
       </c>
@@ -4077,7 +4086,7 @@
       </c>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>158</v>
       </c>
@@ -4092,7 +4101,7 @@
       </c>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>158</v>
       </c>
@@ -4107,7 +4116,7 @@
       </c>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>158</v>
       </c>
@@ -4122,7 +4131,7 @@
       </c>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>158</v>
       </c>
@@ -4137,7 +4146,7 @@
       </c>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>158</v>
       </c>
@@ -4152,7 +4161,7 @@
       </c>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>158</v>
       </c>
@@ -4167,7 +4176,7 @@
       </c>
       <c r="E190" s="3"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>158</v>
       </c>
@@ -4182,7 +4191,7 @@
       </c>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>158</v>
       </c>
@@ -4197,7 +4206,7 @@
       </c>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>158</v>
       </c>
@@ -4212,7 +4221,7 @@
       </c>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>158</v>
       </c>
@@ -4227,7 +4236,7 @@
       </c>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>158</v>
       </c>
@@ -4242,7 +4251,7 @@
       </c>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>158</v>
       </c>
@@ -4257,7 +4266,7 @@
       </c>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>158</v>
       </c>
@@ -4272,7 +4281,7 @@
       </c>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>158</v>
       </c>
@@ -4287,7 +4296,7 @@
       </c>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>158</v>
       </c>
@@ -4302,7 +4311,7 @@
       </c>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>158</v>
       </c>
@@ -4317,7 +4326,7 @@
       </c>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>158</v>
       </c>
@@ -4332,7 +4341,7 @@
       </c>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>158</v>
       </c>
@@ -4347,7 +4356,7 @@
       </c>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>158</v>
       </c>
@@ -4362,7 +4371,7 @@
       </c>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>158</v>
       </c>
@@ -4377,7 +4386,7 @@
       </c>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>158</v>
       </c>
@@ -4392,7 +4401,7 @@
       </c>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>158</v>
       </c>
@@ -4407,7 +4416,7 @@
       </c>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>158</v>
       </c>
@@ -4422,7 +4431,7 @@
       </c>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>158</v>
       </c>
@@ -4437,7 +4446,7 @@
       </c>
       <c r="E208" s="3"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>158</v>
       </c>
@@ -4452,7 +4461,7 @@
       </c>
       <c r="E209" s="3"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>158</v>
       </c>
@@ -4467,7 +4476,7 @@
       </c>
       <c r="E210" s="3"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>158</v>
       </c>
@@ -4482,7 +4491,7 @@
       </c>
       <c r="E211" s="3"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>158</v>
       </c>
@@ -4497,7 +4506,7 @@
       </c>
       <c r="E212" s="3"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>158</v>
       </c>
@@ -4512,7 +4521,7 @@
       </c>
       <c r="E213" s="3"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>158</v>
       </c>
@@ -4527,7 +4536,7 @@
       </c>
       <c r="E214" s="3"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>158</v>
       </c>
@@ -4542,7 +4551,7 @@
       </c>
       <c r="E215" s="3"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>158</v>
       </c>
@@ -4557,7 +4566,7 @@
       </c>
       <c r="E216" s="3"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>158</v>
       </c>
@@ -4572,7 +4581,7 @@
       </c>
       <c r="E217" s="3"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>158</v>
       </c>
@@ -4587,7 +4596,7 @@
       </c>
       <c r="E218" s="3"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>158</v>
       </c>
@@ -4602,7 +4611,7 @@
       </c>
       <c r="E219" s="3"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>158</v>
       </c>
@@ -4618,15 +4627,15 @@
       <c r="E220" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E220"/>
+  <autoFilter ref="A1:E220" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4666,7 +4675,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -4677,7 +4686,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -4953,15 +4962,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C29"/>
+  <autoFilter ref="A1:C29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4979,7 +4988,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -4990,7 +4999,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
@@ -5035,7 +5044,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DB23D5-7F64-4588-837A-A60304EF332D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1997ED2E-3978-4C47-99D4-4B542B74146C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="296">
   <si>
     <t>Level</t>
   </si>
@@ -1656,7 +1656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -1669,9 +1669,11 @@
       <c r="D23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
@@ -1684,9 +1686,11 @@
       <c r="D24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -1699,9 +1703,11 @@
       <c r="D25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -1714,9 +1720,11 @@
       <c r="D26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -1729,7 +1737,9 @@
       <c r="D27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
@@ -1791,7 +1801,7 @@
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
@@ -1806,7 +1816,7 @@
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
@@ -1821,7 +1831,7 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>26</v>
       </c>
@@ -1836,7 +1846,7 @@
       </c>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>26</v>
       </c>
@@ -1851,7 +1861,7 @@
       </c>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>26</v>
       </c>

--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -3,14 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1997ED2E-3978-4C47-99D4-4B542B74146C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAE2EC6-B12E-45D9-B1A7-4701C497F8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
     <sheet name="Topics &amp; Subtopics" sheetId="2" r:id="rId2"/>
-    <sheet name="Progress" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Topics &amp; Subtopics'!$A$1:$C$29</definedName>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="288">
   <si>
     <t>Level</t>
   </si>
@@ -884,30 +883,6 @@
   </si>
   <si>
     <t>Images/containers; Dockerfile; commands; ports; environment; Compose; Spring Boot + DB</t>
-  </si>
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Completed — 17/17 practice problems</t>
-  </si>
-  <si>
-    <t>Problem-Solving Patterns</t>
-  </si>
-  <si>
-    <t>In Progress — HashMap: 7 completed, #8 next</t>
-  </si>
-  <si>
-    <t>Core Java</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>DSA</t>
-  </si>
-  <si>
-    <t>Java Developer</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
@@ -1754,9 +1729,11 @@
       <c r="D28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>26</v>
       </c>
@@ -1769,9 +1746,11 @@
       <c r="D29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
@@ -1784,9 +1763,11 @@
       <c r="D30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
@@ -1799,7 +1780,9 @@
       <c r="D31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -4975,86 +4958,4 @@
   <autoFilter ref="A1:C29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAE2EC6-B12E-45D9-B1A7-4701C497F8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB2B5F8-6D0F-48F9-9B42-AAE6FC9CFB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="288">
   <si>
     <t>Level</t>
   </si>
@@ -1797,7 +1797,9 @@
       <c r="D32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">

--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB2B5F8-6D0F-48F9-9B42-AAE6FC9CFB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
-    <sheet name="Topics &amp; Subtopics" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Roadmap" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Topics &amp; Subtopics" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Topics &amp; Subtopics'!$A$1:$C$29</definedName>
@@ -19,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="288">
   <si>
     <t>Level</t>
   </si>
@@ -888,19 +887,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1246,9 +1245,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E220"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1563,7 +1562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -1580,7 +1579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1597,7 +1596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -1614,7 +1613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
@@ -1631,7 +1630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -1648,7 +1647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
@@ -1665,7 +1664,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -1682,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -1699,7 +1698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -1716,7 +1715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>26</v>
       </c>
@@ -1750,7 +1749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
@@ -1767,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
@@ -1784,7 +1783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
@@ -1801,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
@@ -1814,9 +1813,11 @@
       <c r="D33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E33" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>26</v>
       </c>
@@ -1831,7 +1832,7 @@
       </c>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>26</v>
       </c>
@@ -1846,7 +1847,7 @@
       </c>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>26</v>
       </c>
@@ -1861,7 +1862,7 @@
       </c>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>26</v>
       </c>
@@ -1876,7 +1877,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>26</v>
       </c>
@@ -1891,7 +1892,7 @@
       </c>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>26</v>
       </c>
@@ -1906,7 +1907,7 @@
       </c>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>26</v>
       </c>
@@ -1921,7 +1922,7 @@
       </c>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>26</v>
       </c>
@@ -1936,7 +1937,7 @@
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
@@ -1951,7 +1952,7 @@
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>26</v>
       </c>
@@ -1966,7 +1967,7 @@
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>26</v>
       </c>
@@ -1981,7 +1982,7 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>26</v>
       </c>
@@ -1996,7 +1997,7 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>26</v>
       </c>
@@ -2011,7 +2012,7 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>26</v>
       </c>
@@ -2026,7 +2027,7 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>26</v>
       </c>
@@ -2041,7 +2042,7 @@
       </c>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
@@ -2056,7 +2057,7 @@
       </c>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>61</v>
       </c>
@@ -2071,7 +2072,7 @@
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>61</v>
       </c>
@@ -2086,7 +2087,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>61</v>
       </c>
@@ -2101,7 +2102,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>61</v>
       </c>
@@ -2116,7 +2117,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>61</v>
       </c>
@@ -2131,7 +2132,7 @@
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>61</v>
       </c>
@@ -2146,7 +2147,7 @@
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
@@ -2161,7 +2162,7 @@
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
@@ -2176,7 +2177,7 @@
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>61</v>
       </c>
@@ -2191,7 +2192,7 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -2206,7 +2207,7 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>61</v>
       </c>
@@ -2221,7 +2222,7 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
@@ -2236,7 +2237,7 @@
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>61</v>
       </c>
@@ -2251,7 +2252,7 @@
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
@@ -2266,7 +2267,7 @@
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>61</v>
       </c>
@@ -2281,7 +2282,7 @@
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>61</v>
       </c>
@@ -2296,7 +2297,7 @@
       </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -2311,7 +2312,7 @@
       </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>61</v>
       </c>
@@ -2326,7 +2327,7 @@
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>61</v>
       </c>
@@ -2341,7 +2342,7 @@
       </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>61</v>
       </c>
@@ -2356,7 +2357,7 @@
       </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>61</v>
       </c>
@@ -2371,7 +2372,7 @@
       </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>61</v>
       </c>
@@ -2386,7 +2387,7 @@
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>61</v>
       </c>
@@ -2401,7 +2402,7 @@
       </c>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>61</v>
       </c>
@@ -2416,7 +2417,7 @@
       </c>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>61</v>
       </c>
@@ -2431,7 +2432,7 @@
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>61</v>
       </c>
@@ -2446,7 +2447,7 @@
       </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>61</v>
       </c>
@@ -2461,7 +2462,7 @@
       </c>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>61</v>
       </c>
@@ -2476,7 +2477,7 @@
       </c>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>61</v>
       </c>
@@ -2506,7 +2507,7 @@
       </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>61</v>
       </c>
@@ -2521,7 +2522,7 @@
       </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>61</v>
       </c>
@@ -2536,7 +2537,7 @@
       </c>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>61</v>
       </c>
@@ -2551,7 +2552,7 @@
       </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>61</v>
       </c>
@@ -2566,7 +2567,7 @@
       </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>61</v>
       </c>
@@ -2581,7 +2582,7 @@
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
@@ -2596,7 +2597,7 @@
       </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>61</v>
       </c>
@@ -2611,7 +2612,7 @@
       </c>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>61</v>
       </c>
@@ -2626,7 +2627,7 @@
       </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
@@ -2641,7 +2642,7 @@
       </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>61</v>
       </c>
@@ -2656,7 +2657,7 @@
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>61</v>
       </c>
@@ -2671,7 +2672,7 @@
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>61</v>
       </c>
@@ -2686,7 +2687,7 @@
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>61</v>
       </c>
@@ -2701,7 +2702,7 @@
       </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>61</v>
       </c>
@@ -2716,7 +2717,7 @@
       </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>61</v>
       </c>
@@ -2731,7 +2732,7 @@
       </c>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>61</v>
       </c>
@@ -2746,7 +2747,7 @@
       </c>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>61</v>
       </c>
@@ -2761,7 +2762,7 @@
       </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>61</v>
       </c>
@@ -2776,7 +2777,7 @@
       </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>61</v>
       </c>
@@ -2791,7 +2792,7 @@
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>61</v>
       </c>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>61</v>
       </c>
@@ -2821,7 +2822,7 @@
       </c>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>120</v>
       </c>
@@ -2836,7 +2837,7 @@
       </c>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>120</v>
       </c>
@@ -2851,7 +2852,7 @@
       </c>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>120</v>
       </c>
@@ -2866,7 +2867,7 @@
       </c>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
@@ -2881,7 +2882,7 @@
       </c>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>120</v>
       </c>
@@ -2896,7 +2897,7 @@
       </c>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>120</v>
       </c>
@@ -2911,7 +2912,7 @@
       </c>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>120</v>
       </c>
@@ -2926,7 +2927,7 @@
       </c>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>120</v>
       </c>
@@ -2941,7 +2942,7 @@
       </c>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>120</v>
       </c>
@@ -2956,7 +2957,7 @@
       </c>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>120</v>
       </c>
@@ -2971,7 +2972,7 @@
       </c>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>120</v>
       </c>
@@ -2986,7 +2987,7 @@
       </c>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>120</v>
       </c>
@@ -3001,7 +3002,7 @@
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>120</v>
       </c>
@@ -3016,7 +3017,7 @@
       </c>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>120</v>
       </c>
@@ -3031,7 +3032,7 @@
       </c>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>120</v>
       </c>
@@ -3046,7 +3047,7 @@
       </c>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>120</v>
       </c>
@@ -3061,7 +3062,7 @@
       </c>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>120</v>
       </c>
@@ -3076,7 +3077,7 @@
       </c>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>120</v>
       </c>
@@ -3091,7 +3092,7 @@
       </c>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>120</v>
       </c>
@@ -3106,7 +3107,7 @@
       </c>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>120</v>
       </c>
@@ -3121,7 +3122,7 @@
       </c>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>120</v>
       </c>
@@ -3136,7 +3137,7 @@
       </c>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
@@ -3151,7 +3152,7 @@
       </c>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>120</v>
       </c>
@@ -3166,7 +3167,7 @@
       </c>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>120</v>
       </c>
@@ -3181,7 +3182,7 @@
       </c>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -3196,7 +3197,7 @@
       </c>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
@@ -3211,7 +3212,7 @@
       </c>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>120</v>
       </c>
@@ -3226,7 +3227,7 @@
       </c>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>120</v>
       </c>
@@ -3241,7 +3242,7 @@
       </c>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>120</v>
       </c>
@@ -3256,7 +3257,7 @@
       </c>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>120</v>
       </c>
@@ -3271,7 +3272,7 @@
       </c>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>120</v>
       </c>
@@ -3286,7 +3287,7 @@
       </c>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>120</v>
       </c>
@@ -3301,7 +3302,7 @@
       </c>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
@@ -3316,7 +3317,7 @@
       </c>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>158</v>
       </c>
@@ -3331,7 +3332,7 @@
       </c>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>158</v>
       </c>
@@ -3346,7 +3347,7 @@
       </c>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>158</v>
       </c>
@@ -3361,7 +3362,7 @@
       </c>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>158</v>
       </c>
@@ -3376,7 +3377,7 @@
       </c>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>158</v>
       </c>
@@ -3391,7 +3392,7 @@
       </c>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>158</v>
       </c>
@@ -3406,7 +3407,7 @@
       </c>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>158</v>
       </c>
@@ -3421,7 +3422,7 @@
       </c>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>158</v>
       </c>
@@ -3436,7 +3437,7 @@
       </c>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>158</v>
       </c>
@@ -3451,7 +3452,7 @@
       </c>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>158</v>
       </c>
@@ -3466,7 +3467,7 @@
       </c>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>158</v>
       </c>
@@ -3481,7 +3482,7 @@
       </c>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>158</v>
       </c>
@@ -3496,7 +3497,7 @@
       </c>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>158</v>
       </c>
@@ -3511,7 +3512,7 @@
       </c>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>158</v>
       </c>
@@ -3526,7 +3527,7 @@
       </c>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
@@ -3541,7 +3542,7 @@
       </c>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>158</v>
       </c>
@@ -3556,7 +3557,7 @@
       </c>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>158</v>
       </c>
@@ -3571,7 +3572,7 @@
       </c>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>158</v>
       </c>
@@ -3586,7 +3587,7 @@
       </c>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>158</v>
       </c>
@@ -3601,7 +3602,7 @@
       </c>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>158</v>
       </c>
@@ -3616,7 +3617,7 @@
       </c>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>158</v>
       </c>
@@ -3631,7 +3632,7 @@
       </c>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>158</v>
       </c>
@@ -3646,7 +3647,7 @@
       </c>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
@@ -3661,7 +3662,7 @@
       </c>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>158</v>
       </c>
@@ -3676,7 +3677,7 @@
       </c>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>158</v>
       </c>
@@ -3691,7 +3692,7 @@
       </c>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>158</v>
       </c>
@@ -3706,7 +3707,7 @@
       </c>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>158</v>
       </c>
@@ -3721,7 +3722,7 @@
       </c>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>158</v>
       </c>
@@ -3736,7 +3737,7 @@
       </c>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>158</v>
       </c>
@@ -3751,7 +3752,7 @@
       </c>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>158</v>
       </c>
@@ -3766,7 +3767,7 @@
       </c>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>158</v>
       </c>
@@ -3781,7 +3782,7 @@
       </c>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>158</v>
       </c>
@@ -3796,7 +3797,7 @@
       </c>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>158</v>
       </c>
@@ -3811,7 +3812,7 @@
       </c>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -3826,7 +3827,7 @@
       </c>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>158</v>
       </c>
@@ -3841,7 +3842,7 @@
       </c>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>158</v>
       </c>
@@ -3856,7 +3857,7 @@
       </c>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>158</v>
       </c>
@@ -3871,7 +3872,7 @@
       </c>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>158</v>
       </c>
@@ -3886,7 +3887,7 @@
       </c>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>158</v>
       </c>
@@ -3901,7 +3902,7 @@
       </c>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>158</v>
       </c>
@@ -3916,7 +3917,7 @@
       </c>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>158</v>
       </c>
@@ -3931,7 +3932,7 @@
       </c>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>158</v>
       </c>
@@ -3946,7 +3947,7 @@
       </c>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>158</v>
       </c>
@@ -3961,7 +3962,7 @@
       </c>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>158</v>
       </c>
@@ -3976,7 +3977,7 @@
       </c>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>158</v>
       </c>
@@ -3991,7 +3992,7 @@
       </c>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>158</v>
       </c>
@@ -4006,7 +4007,7 @@
       </c>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>158</v>
       </c>
@@ -4021,7 +4022,7 @@
       </c>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>158</v>
       </c>
@@ -4036,7 +4037,7 @@
       </c>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>158</v>
       </c>
@@ -4051,7 +4052,7 @@
       </c>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>158</v>
       </c>
@@ -4066,7 +4067,7 @@
       </c>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>158</v>
       </c>
@@ -4081,7 +4082,7 @@
       </c>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>158</v>
       </c>
@@ -4096,7 +4097,7 @@
       </c>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>158</v>
       </c>
@@ -4111,7 +4112,7 @@
       </c>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>158</v>
       </c>
@@ -4126,7 +4127,7 @@
       </c>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>158</v>
       </c>
@@ -4141,7 +4142,7 @@
       </c>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>158</v>
       </c>
@@ -4156,7 +4157,7 @@
       </c>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>158</v>
       </c>
@@ -4171,7 +4172,7 @@
       </c>
       <c r="E190" s="3"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>158</v>
       </c>
@@ -4186,7 +4187,7 @@
       </c>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>158</v>
       </c>
@@ -4201,7 +4202,7 @@
       </c>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>158</v>
       </c>
@@ -4216,7 +4217,7 @@
       </c>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>158</v>
       </c>
@@ -4231,7 +4232,7 @@
       </c>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>158</v>
       </c>
@@ -4246,7 +4247,7 @@
       </c>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>158</v>
       </c>
@@ -4261,7 +4262,7 @@
       </c>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>158</v>
       </c>
@@ -4276,7 +4277,7 @@
       </c>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>158</v>
       </c>
@@ -4291,7 +4292,7 @@
       </c>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>158</v>
       </c>
@@ -4306,7 +4307,7 @@
       </c>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>158</v>
       </c>
@@ -4321,7 +4322,7 @@
       </c>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>158</v>
       </c>
@@ -4336,7 +4337,7 @@
       </c>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>158</v>
       </c>
@@ -4351,7 +4352,7 @@
       </c>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>158</v>
       </c>
@@ -4366,7 +4367,7 @@
       </c>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>158</v>
       </c>
@@ -4381,7 +4382,7 @@
       </c>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>158</v>
       </c>
@@ -4396,7 +4397,7 @@
       </c>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>158</v>
       </c>
@@ -4411,7 +4412,7 @@
       </c>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>158</v>
       </c>
@@ -4426,7 +4427,7 @@
       </c>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>158</v>
       </c>
@@ -4441,7 +4442,7 @@
       </c>
       <c r="E208" s="3"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>158</v>
       </c>
@@ -4456,7 +4457,7 @@
       </c>
       <c r="E209" s="3"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>158</v>
       </c>
@@ -4471,7 +4472,7 @@
       </c>
       <c r="E210" s="3"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>158</v>
       </c>
@@ -4486,7 +4487,7 @@
       </c>
       <c r="E211" s="3"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>158</v>
       </c>
@@ -4501,7 +4502,7 @@
       </c>
       <c r="E212" s="3"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>158</v>
       </c>
@@ -4516,7 +4517,7 @@
       </c>
       <c r="E213" s="3"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>158</v>
       </c>
@@ -4531,7 +4532,7 @@
       </c>
       <c r="E214" s="3"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>158</v>
       </c>
@@ -4546,7 +4547,7 @@
       </c>
       <c r="E215" s="3"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>158</v>
       </c>
@@ -4561,7 +4562,7 @@
       </c>
       <c r="E216" s="3"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>158</v>
       </c>
@@ -4576,7 +4577,7 @@
       </c>
       <c r="E217" s="3"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>158</v>
       </c>
@@ -4591,7 +4592,7 @@
       </c>
       <c r="E218" s="3"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>158</v>
       </c>
@@ -4606,7 +4607,7 @@
       </c>
       <c r="E219" s="3"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>158</v>
       </c>
@@ -4622,15 +4623,15 @@
       <c r="E220" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E220" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4670,7 +4671,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -4681,7 +4682,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -4957,7 +4958,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:C29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094BE57E-1E2E-497B-9B9A-398F3C083BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Roadmap" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Topics &amp; Subtopics" state="visible" r:id="rId5"/>
+    <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
+    <sheet name="Topics &amp; Subtopics" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Topics &amp; Subtopics'!$A$1:$C$29</definedName>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="288">
   <si>
     <t>Level</t>
   </si>
@@ -887,19 +888,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1245,9 +1246,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E220"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1817,7 +1818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>26</v>
       </c>
@@ -1830,7 +1831,9 @@
       <c r="D34" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="3"/>
+      <c r="E34" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -1937,7 +1940,7 @@
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
@@ -1952,7 +1955,7 @@
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>26</v>
       </c>
@@ -1967,7 +1970,7 @@
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>26</v>
       </c>
@@ -1982,7 +1985,7 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>26</v>
       </c>
@@ -1997,7 +2000,7 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>26</v>
       </c>
@@ -2012,7 +2015,7 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>26</v>
       </c>
@@ -2027,7 +2030,7 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>26</v>
       </c>
@@ -2042,7 +2045,7 @@
       </c>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
@@ -2057,7 +2060,7 @@
       </c>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>61</v>
       </c>
@@ -2072,7 +2075,7 @@
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>61</v>
       </c>
@@ -2087,7 +2090,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>61</v>
       </c>
@@ -2102,7 +2105,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>61</v>
       </c>
@@ -2117,7 +2120,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>61</v>
       </c>
@@ -2132,7 +2135,7 @@
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>61</v>
       </c>
@@ -2147,7 +2150,7 @@
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
@@ -2162,7 +2165,7 @@
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
@@ -2177,7 +2180,7 @@
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>61</v>
       </c>
@@ -2192,7 +2195,7 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -2207,7 +2210,7 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>61</v>
       </c>
@@ -2222,7 +2225,7 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
@@ -2237,7 +2240,7 @@
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>61</v>
       </c>
@@ -2252,7 +2255,7 @@
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
@@ -2267,7 +2270,7 @@
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>61</v>
       </c>
@@ -2282,7 +2285,7 @@
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>61</v>
       </c>
@@ -2297,7 +2300,7 @@
       </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -2312,7 +2315,7 @@
       </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>61</v>
       </c>
@@ -2327,7 +2330,7 @@
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>61</v>
       </c>
@@ -2342,7 +2345,7 @@
       </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>61</v>
       </c>
@@ -2357,7 +2360,7 @@
       </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>61</v>
       </c>
@@ -2372,7 +2375,7 @@
       </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>61</v>
       </c>
@@ -2387,7 +2390,7 @@
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>61</v>
       </c>
@@ -2402,7 +2405,7 @@
       </c>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>61</v>
       </c>
@@ -2417,7 +2420,7 @@
       </c>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>61</v>
       </c>
@@ -2432,7 +2435,7 @@
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>61</v>
       </c>
@@ -2447,7 +2450,7 @@
       </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>61</v>
       </c>
@@ -2462,7 +2465,7 @@
       </c>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>61</v>
       </c>
@@ -2477,7 +2480,7 @@
       </c>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -2492,7 +2495,7 @@
       </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>61</v>
       </c>
@@ -2507,7 +2510,7 @@
       </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>61</v>
       </c>
@@ -2522,7 +2525,7 @@
       </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>61</v>
       </c>
@@ -2537,7 +2540,7 @@
       </c>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>61</v>
       </c>
@@ -2552,7 +2555,7 @@
       </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>61</v>
       </c>
@@ -2567,7 +2570,7 @@
       </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>61</v>
       </c>
@@ -2582,7 +2585,7 @@
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
@@ -2597,7 +2600,7 @@
       </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>61</v>
       </c>
@@ -2612,7 +2615,7 @@
       </c>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>61</v>
       </c>
@@ -2627,7 +2630,7 @@
       </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
@@ -2642,7 +2645,7 @@
       </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>61</v>
       </c>
@@ -2657,7 +2660,7 @@
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>61</v>
       </c>
@@ -2672,7 +2675,7 @@
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>61</v>
       </c>
@@ -2687,7 +2690,7 @@
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>61</v>
       </c>
@@ -2702,7 +2705,7 @@
       </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>61</v>
       </c>
@@ -2717,7 +2720,7 @@
       </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>61</v>
       </c>
@@ -2732,7 +2735,7 @@
       </c>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>61</v>
       </c>
@@ -2747,7 +2750,7 @@
       </c>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>61</v>
       </c>
@@ -2762,7 +2765,7 @@
       </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>61</v>
       </c>
@@ -2777,7 +2780,7 @@
       </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>61</v>
       </c>
@@ -2792,7 +2795,7 @@
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>61</v>
       </c>
@@ -2807,7 +2810,7 @@
       </c>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>61</v>
       </c>
@@ -2822,7 +2825,7 @@
       </c>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>120</v>
       </c>
@@ -2837,7 +2840,7 @@
       </c>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>120</v>
       </c>
@@ -2852,7 +2855,7 @@
       </c>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>120</v>
       </c>
@@ -2867,7 +2870,7 @@
       </c>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
@@ -2882,7 +2885,7 @@
       </c>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>120</v>
       </c>
@@ -2897,7 +2900,7 @@
       </c>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>120</v>
       </c>
@@ -2912,7 +2915,7 @@
       </c>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>120</v>
       </c>
@@ -2927,7 +2930,7 @@
       </c>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>120</v>
       </c>
@@ -2942,7 +2945,7 @@
       </c>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>120</v>
       </c>
@@ -2957,7 +2960,7 @@
       </c>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>120</v>
       </c>
@@ -2972,7 +2975,7 @@
       </c>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>120</v>
       </c>
@@ -2987,7 +2990,7 @@
       </c>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>120</v>
       </c>
@@ -3002,7 +3005,7 @@
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>120</v>
       </c>
@@ -3017,7 +3020,7 @@
       </c>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>120</v>
       </c>
@@ -3032,7 +3035,7 @@
       </c>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>120</v>
       </c>
@@ -3047,7 +3050,7 @@
       </c>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>120</v>
       </c>
@@ -3062,7 +3065,7 @@
       </c>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>120</v>
       </c>
@@ -3077,7 +3080,7 @@
       </c>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>120</v>
       </c>
@@ -3092,7 +3095,7 @@
       </c>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>120</v>
       </c>
@@ -3107,7 +3110,7 @@
       </c>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>120</v>
       </c>
@@ -3122,7 +3125,7 @@
       </c>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>120</v>
       </c>
@@ -3137,7 +3140,7 @@
       </c>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
@@ -3152,7 +3155,7 @@
       </c>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>120</v>
       </c>
@@ -3167,7 +3170,7 @@
       </c>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>120</v>
       </c>
@@ -3182,7 +3185,7 @@
       </c>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -3197,7 +3200,7 @@
       </c>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
@@ -3212,7 +3215,7 @@
       </c>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>120</v>
       </c>
@@ -3227,7 +3230,7 @@
       </c>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>120</v>
       </c>
@@ -3242,7 +3245,7 @@
       </c>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>120</v>
       </c>
@@ -3257,7 +3260,7 @@
       </c>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>120</v>
       </c>
@@ -3272,7 +3275,7 @@
       </c>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>120</v>
       </c>
@@ -3287,7 +3290,7 @@
       </c>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>120</v>
       </c>
@@ -3302,7 +3305,7 @@
       </c>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
@@ -3317,7 +3320,7 @@
       </c>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>158</v>
       </c>
@@ -3332,7 +3335,7 @@
       </c>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>158</v>
       </c>
@@ -3347,7 +3350,7 @@
       </c>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>158</v>
       </c>
@@ -3362,7 +3365,7 @@
       </c>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>158</v>
       </c>
@@ -3377,7 +3380,7 @@
       </c>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>158</v>
       </c>
@@ -3392,7 +3395,7 @@
       </c>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>158</v>
       </c>
@@ -3407,7 +3410,7 @@
       </c>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>158</v>
       </c>
@@ -3422,7 +3425,7 @@
       </c>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>158</v>
       </c>
@@ -3437,7 +3440,7 @@
       </c>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>158</v>
       </c>
@@ -3452,7 +3455,7 @@
       </c>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>158</v>
       </c>
@@ -3467,7 +3470,7 @@
       </c>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>158</v>
       </c>
@@ -3482,7 +3485,7 @@
       </c>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>158</v>
       </c>
@@ -3497,7 +3500,7 @@
       </c>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>158</v>
       </c>
@@ -3512,7 +3515,7 @@
       </c>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>158</v>
       </c>
@@ -3527,7 +3530,7 @@
       </c>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
@@ -3542,7 +3545,7 @@
       </c>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>158</v>
       </c>
@@ -3557,7 +3560,7 @@
       </c>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>158</v>
       </c>
@@ -3572,7 +3575,7 @@
       </c>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>158</v>
       </c>
@@ -3587,7 +3590,7 @@
       </c>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>158</v>
       </c>
@@ -3602,7 +3605,7 @@
       </c>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>158</v>
       </c>
@@ -3617,7 +3620,7 @@
       </c>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>158</v>
       </c>
@@ -3632,7 +3635,7 @@
       </c>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>158</v>
       </c>
@@ -3647,7 +3650,7 @@
       </c>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
@@ -3662,7 +3665,7 @@
       </c>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>158</v>
       </c>
@@ -3677,7 +3680,7 @@
       </c>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>158</v>
       </c>
@@ -3692,7 +3695,7 @@
       </c>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>158</v>
       </c>
@@ -3707,7 +3710,7 @@
       </c>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>158</v>
       </c>
@@ -3722,7 +3725,7 @@
       </c>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>158</v>
       </c>
@@ -3737,7 +3740,7 @@
       </c>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>158</v>
       </c>
@@ -3752,7 +3755,7 @@
       </c>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>158</v>
       </c>
@@ -3767,7 +3770,7 @@
       </c>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>158</v>
       </c>
@@ -3782,7 +3785,7 @@
       </c>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>158</v>
       </c>
@@ -3797,7 +3800,7 @@
       </c>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>158</v>
       </c>
@@ -3812,7 +3815,7 @@
       </c>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -3827,7 +3830,7 @@
       </c>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>158</v>
       </c>
@@ -3842,7 +3845,7 @@
       </c>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>158</v>
       </c>
@@ -3857,7 +3860,7 @@
       </c>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>158</v>
       </c>
@@ -3872,7 +3875,7 @@
       </c>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>158</v>
       </c>
@@ -3887,7 +3890,7 @@
       </c>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>158</v>
       </c>
@@ -3902,7 +3905,7 @@
       </c>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>158</v>
       </c>
@@ -3917,7 +3920,7 @@
       </c>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>158</v>
       </c>
@@ -3932,7 +3935,7 @@
       </c>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>158</v>
       </c>
@@ -3947,7 +3950,7 @@
       </c>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>158</v>
       </c>
@@ -3962,7 +3965,7 @@
       </c>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>158</v>
       </c>
@@ -3977,7 +3980,7 @@
       </c>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>158</v>
       </c>
@@ -3992,7 +3995,7 @@
       </c>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>158</v>
       </c>
@@ -4007,7 +4010,7 @@
       </c>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>158</v>
       </c>
@@ -4022,7 +4025,7 @@
       </c>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>158</v>
       </c>
@@ -4037,7 +4040,7 @@
       </c>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>158</v>
       </c>
@@ -4052,7 +4055,7 @@
       </c>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>158</v>
       </c>
@@ -4067,7 +4070,7 @@
       </c>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>158</v>
       </c>
@@ -4082,7 +4085,7 @@
       </c>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>158</v>
       </c>
@@ -4097,7 +4100,7 @@
       </c>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>158</v>
       </c>
@@ -4112,7 +4115,7 @@
       </c>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>158</v>
       </c>
@@ -4127,7 +4130,7 @@
       </c>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>158</v>
       </c>
@@ -4142,7 +4145,7 @@
       </c>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>158</v>
       </c>
@@ -4157,7 +4160,7 @@
       </c>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>158</v>
       </c>
@@ -4172,7 +4175,7 @@
       </c>
       <c r="E190" s="3"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>158</v>
       </c>
@@ -4187,7 +4190,7 @@
       </c>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>158</v>
       </c>
@@ -4202,7 +4205,7 @@
       </c>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>158</v>
       </c>
@@ -4217,7 +4220,7 @@
       </c>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>158</v>
       </c>
@@ -4232,7 +4235,7 @@
       </c>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>158</v>
       </c>
@@ -4247,7 +4250,7 @@
       </c>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>158</v>
       </c>
@@ -4262,7 +4265,7 @@
       </c>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>158</v>
       </c>
@@ -4277,7 +4280,7 @@
       </c>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>158</v>
       </c>
@@ -4292,7 +4295,7 @@
       </c>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>158</v>
       </c>
@@ -4307,7 +4310,7 @@
       </c>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>158</v>
       </c>
@@ -4322,7 +4325,7 @@
       </c>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>158</v>
       </c>
@@ -4337,7 +4340,7 @@
       </c>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>158</v>
       </c>
@@ -4352,7 +4355,7 @@
       </c>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>158</v>
       </c>
@@ -4367,7 +4370,7 @@
       </c>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>158</v>
       </c>
@@ -4382,7 +4385,7 @@
       </c>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>158</v>
       </c>
@@ -4397,7 +4400,7 @@
       </c>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>158</v>
       </c>
@@ -4412,7 +4415,7 @@
       </c>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>158</v>
       </c>
@@ -4427,7 +4430,7 @@
       </c>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>158</v>
       </c>
@@ -4442,7 +4445,7 @@
       </c>
       <c r="E208" s="3"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>158</v>
       </c>
@@ -4457,7 +4460,7 @@
       </c>
       <c r="E209" s="3"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>158</v>
       </c>
@@ -4472,7 +4475,7 @@
       </c>
       <c r="E210" s="3"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>158</v>
       </c>
@@ -4487,7 +4490,7 @@
       </c>
       <c r="E211" s="3"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>158</v>
       </c>
@@ -4502,7 +4505,7 @@
       </c>
       <c r="E212" s="3"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>158</v>
       </c>
@@ -4517,7 +4520,7 @@
       </c>
       <c r="E213" s="3"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>158</v>
       </c>
@@ -4532,7 +4535,7 @@
       </c>
       <c r="E214" s="3"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>158</v>
       </c>
@@ -4547,7 +4550,7 @@
       </c>
       <c r="E215" s="3"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>158</v>
       </c>
@@ -4562,7 +4565,7 @@
       </c>
       <c r="E216" s="3"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>158</v>
       </c>
@@ -4577,7 +4580,7 @@
       </c>
       <c r="E217" s="3"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>158</v>
       </c>
@@ -4592,7 +4595,7 @@
       </c>
       <c r="E218" s="3"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>158</v>
       </c>
@@ -4607,7 +4610,7 @@
       </c>
       <c r="E219" s="3"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>158</v>
       </c>
@@ -4623,15 +4626,15 @@
       <c r="E220" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E220"/>
+  <autoFilter ref="A1:E220" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4671,7 +4674,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -4682,7 +4685,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -4958,7 +4961,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C29"/>
+  <autoFilter ref="A1:C29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094BE57E-1E2E-497B-9B9A-398F3C083BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
-    <sheet name="Topics &amp; Subtopics" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Roadmap" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Topics &amp; Subtopics" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Topics &amp; Subtopics'!$A$1:$C$29</definedName>
@@ -19,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="288">
   <si>
     <t>Level</t>
   </si>
@@ -888,19 +887,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1246,9 +1245,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E220"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1818,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>26</v>
       </c>
@@ -1848,7 +1847,9 @@
       <c r="D35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
@@ -1863,7 +1864,9 @@
       <c r="D36" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
@@ -1940,7 +1943,7 @@
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
@@ -1955,7 +1958,7 @@
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>26</v>
       </c>
@@ -1970,7 +1973,7 @@
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>26</v>
       </c>
@@ -1985,7 +1988,7 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>26</v>
       </c>
@@ -2000,7 +2003,7 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>26</v>
       </c>
@@ -2015,7 +2018,7 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>26</v>
       </c>
@@ -2030,7 +2033,7 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>26</v>
       </c>
@@ -2045,7 +2048,7 @@
       </c>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
@@ -2060,7 +2063,7 @@
       </c>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>61</v>
       </c>
@@ -2075,7 +2078,7 @@
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>61</v>
       </c>
@@ -2090,7 +2093,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>61</v>
       </c>
@@ -2105,7 +2108,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>61</v>
       </c>
@@ -2120,7 +2123,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>61</v>
       </c>
@@ -2135,7 +2138,7 @@
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>61</v>
       </c>
@@ -2150,7 +2153,7 @@
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
@@ -2165,7 +2168,7 @@
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
@@ -2180,7 +2183,7 @@
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>61</v>
       </c>
@@ -2195,7 +2198,7 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -2210,7 +2213,7 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>61</v>
       </c>
@@ -2225,7 +2228,7 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
@@ -2240,7 +2243,7 @@
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2258,7 @@
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
@@ -2270,7 +2273,7 @@
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>61</v>
       </c>
@@ -2285,7 +2288,7 @@
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>61</v>
       </c>
@@ -2300,7 +2303,7 @@
       </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -2315,7 +2318,7 @@
       </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>61</v>
       </c>
@@ -2330,7 +2333,7 @@
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>61</v>
       </c>
@@ -2345,7 +2348,7 @@
       </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>61</v>
       </c>
@@ -2360,7 +2363,7 @@
       </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>61</v>
       </c>
@@ -2375,7 +2378,7 @@
       </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>61</v>
       </c>
@@ -2390,7 +2393,7 @@
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>61</v>
       </c>
@@ -2405,7 +2408,7 @@
       </c>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>61</v>
       </c>
@@ -2420,7 +2423,7 @@
       </c>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>61</v>
       </c>
@@ -2435,7 +2438,7 @@
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>61</v>
       </c>
@@ -2450,7 +2453,7 @@
       </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>61</v>
       </c>
@@ -2465,7 +2468,7 @@
       </c>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>61</v>
       </c>
@@ -2480,7 +2483,7 @@
       </c>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -2495,7 +2498,7 @@
       </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>61</v>
       </c>
@@ -2510,7 +2513,7 @@
       </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>61</v>
       </c>
@@ -2525,7 +2528,7 @@
       </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>61</v>
       </c>
@@ -2540,7 +2543,7 @@
       </c>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>61</v>
       </c>
@@ -2555,7 +2558,7 @@
       </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>61</v>
       </c>
@@ -2570,7 +2573,7 @@
       </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>61</v>
       </c>
@@ -2585,7 +2588,7 @@
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
@@ -2600,7 +2603,7 @@
       </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>61</v>
       </c>
@@ -2615,7 +2618,7 @@
       </c>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>61</v>
       </c>
@@ -2630,7 +2633,7 @@
       </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
@@ -2645,7 +2648,7 @@
       </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>61</v>
       </c>
@@ -2660,7 +2663,7 @@
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>61</v>
       </c>
@@ -2675,7 +2678,7 @@
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>61</v>
       </c>
@@ -2690,7 +2693,7 @@
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>61</v>
       </c>
@@ -2705,7 +2708,7 @@
       </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>61</v>
       </c>
@@ -2720,7 +2723,7 @@
       </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>61</v>
       </c>
@@ -2735,7 +2738,7 @@
       </c>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>61</v>
       </c>
@@ -2750,7 +2753,7 @@
       </c>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>61</v>
       </c>
@@ -2765,7 +2768,7 @@
       </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>61</v>
       </c>
@@ -2780,7 +2783,7 @@
       </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>61</v>
       </c>
@@ -2795,7 +2798,7 @@
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>61</v>
       </c>
@@ -2810,7 +2813,7 @@
       </c>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>61</v>
       </c>
@@ -2825,7 +2828,7 @@
       </c>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>120</v>
       </c>
@@ -2840,7 +2843,7 @@
       </c>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>120</v>
       </c>
@@ -2855,7 +2858,7 @@
       </c>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>120</v>
       </c>
@@ -2870,7 +2873,7 @@
       </c>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
@@ -2885,7 +2888,7 @@
       </c>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>120</v>
       </c>
@@ -2900,7 +2903,7 @@
       </c>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>120</v>
       </c>
@@ -2915,7 +2918,7 @@
       </c>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>120</v>
       </c>
@@ -2930,7 +2933,7 @@
       </c>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>120</v>
       </c>
@@ -2945,7 +2948,7 @@
       </c>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>120</v>
       </c>
@@ -2960,7 +2963,7 @@
       </c>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>120</v>
       </c>
@@ -2975,7 +2978,7 @@
       </c>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>120</v>
       </c>
@@ -2990,7 +2993,7 @@
       </c>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>120</v>
       </c>
@@ -3005,7 +3008,7 @@
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>120</v>
       </c>
@@ -3020,7 +3023,7 @@
       </c>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>120</v>
       </c>
@@ -3035,7 +3038,7 @@
       </c>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>120</v>
       </c>
@@ -3050,7 +3053,7 @@
       </c>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>120</v>
       </c>
@@ -3065,7 +3068,7 @@
       </c>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>120</v>
       </c>
@@ -3080,7 +3083,7 @@
       </c>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>120</v>
       </c>
@@ -3095,7 +3098,7 @@
       </c>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>120</v>
       </c>
@@ -3110,7 +3113,7 @@
       </c>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>120</v>
       </c>
@@ -3125,7 +3128,7 @@
       </c>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>120</v>
       </c>
@@ -3140,7 +3143,7 @@
       </c>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
@@ -3155,7 +3158,7 @@
       </c>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>120</v>
       </c>
@@ -3170,7 +3173,7 @@
       </c>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>120</v>
       </c>
@@ -3185,7 +3188,7 @@
       </c>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -3200,7 +3203,7 @@
       </c>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
@@ -3215,7 +3218,7 @@
       </c>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>120</v>
       </c>
@@ -3230,7 +3233,7 @@
       </c>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>120</v>
       </c>
@@ -3245,7 +3248,7 @@
       </c>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>120</v>
       </c>
@@ -3260,7 +3263,7 @@
       </c>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>120</v>
       </c>
@@ -3275,7 +3278,7 @@
       </c>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>120</v>
       </c>
@@ -3290,7 +3293,7 @@
       </c>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>120</v>
       </c>
@@ -3305,7 +3308,7 @@
       </c>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
@@ -3320,7 +3323,7 @@
       </c>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>158</v>
       </c>
@@ -3335,7 +3338,7 @@
       </c>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>158</v>
       </c>
@@ -3350,7 +3353,7 @@
       </c>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>158</v>
       </c>
@@ -3365,7 +3368,7 @@
       </c>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>158</v>
       </c>
@@ -3380,7 +3383,7 @@
       </c>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>158</v>
       </c>
@@ -3395,7 +3398,7 @@
       </c>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>158</v>
       </c>
@@ -3410,7 +3413,7 @@
       </c>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>158</v>
       </c>
@@ -3425,7 +3428,7 @@
       </c>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>158</v>
       </c>
@@ -3440,7 +3443,7 @@
       </c>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>158</v>
       </c>
@@ -3455,7 +3458,7 @@
       </c>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>158</v>
       </c>
@@ -3470,7 +3473,7 @@
       </c>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>158</v>
       </c>
@@ -3485,7 +3488,7 @@
       </c>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>158</v>
       </c>
@@ -3500,7 +3503,7 @@
       </c>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>158</v>
       </c>
@@ -3515,7 +3518,7 @@
       </c>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>158</v>
       </c>
@@ -3530,7 +3533,7 @@
       </c>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
@@ -3545,7 +3548,7 @@
       </c>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>158</v>
       </c>
@@ -3560,7 +3563,7 @@
       </c>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>158</v>
       </c>
@@ -3575,7 +3578,7 @@
       </c>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>158</v>
       </c>
@@ -3590,7 +3593,7 @@
       </c>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>158</v>
       </c>
@@ -3605,7 +3608,7 @@
       </c>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>158</v>
       </c>
@@ -3620,7 +3623,7 @@
       </c>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>158</v>
       </c>
@@ -3635,7 +3638,7 @@
       </c>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>158</v>
       </c>
@@ -3650,7 +3653,7 @@
       </c>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
@@ -3665,7 +3668,7 @@
       </c>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>158</v>
       </c>
@@ -3680,7 +3683,7 @@
       </c>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>158</v>
       </c>
@@ -3695,7 +3698,7 @@
       </c>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>158</v>
       </c>
@@ -3710,7 +3713,7 @@
       </c>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>158</v>
       </c>
@@ -3725,7 +3728,7 @@
       </c>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>158</v>
       </c>
@@ -3740,7 +3743,7 @@
       </c>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>158</v>
       </c>
@@ -3755,7 +3758,7 @@
       </c>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>158</v>
       </c>
@@ -3770,7 +3773,7 @@
       </c>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>158</v>
       </c>
@@ -3785,7 +3788,7 @@
       </c>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>158</v>
       </c>
@@ -3800,7 +3803,7 @@
       </c>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>158</v>
       </c>
@@ -3815,7 +3818,7 @@
       </c>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -3830,7 +3833,7 @@
       </c>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>158</v>
       </c>
@@ -3845,7 +3848,7 @@
       </c>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>158</v>
       </c>
@@ -3860,7 +3863,7 @@
       </c>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>158</v>
       </c>
@@ -3875,7 +3878,7 @@
       </c>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>158</v>
       </c>
@@ -3890,7 +3893,7 @@
       </c>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>158</v>
       </c>
@@ -3905,7 +3908,7 @@
       </c>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>158</v>
       </c>
@@ -3920,7 +3923,7 @@
       </c>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>158</v>
       </c>
@@ -3935,7 +3938,7 @@
       </c>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>158</v>
       </c>
@@ -3950,7 +3953,7 @@
       </c>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>158</v>
       </c>
@@ -3965,7 +3968,7 @@
       </c>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>158</v>
       </c>
@@ -3980,7 +3983,7 @@
       </c>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>158</v>
       </c>
@@ -3995,7 +3998,7 @@
       </c>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>158</v>
       </c>
@@ -4010,7 +4013,7 @@
       </c>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>158</v>
       </c>
@@ -4025,7 +4028,7 @@
       </c>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>158</v>
       </c>
@@ -4040,7 +4043,7 @@
       </c>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>158</v>
       </c>
@@ -4055,7 +4058,7 @@
       </c>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>158</v>
       </c>
@@ -4070,7 +4073,7 @@
       </c>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>158</v>
       </c>
@@ -4085,7 +4088,7 @@
       </c>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>158</v>
       </c>
@@ -4100,7 +4103,7 @@
       </c>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>158</v>
       </c>
@@ -4115,7 +4118,7 @@
       </c>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>158</v>
       </c>
@@ -4130,7 +4133,7 @@
       </c>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>158</v>
       </c>
@@ -4145,7 +4148,7 @@
       </c>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>158</v>
       </c>
@@ -4160,7 +4163,7 @@
       </c>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>158</v>
       </c>
@@ -4175,7 +4178,7 @@
       </c>
       <c r="E190" s="3"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>158</v>
       </c>
@@ -4190,7 +4193,7 @@
       </c>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>158</v>
       </c>
@@ -4205,7 +4208,7 @@
       </c>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>158</v>
       </c>
@@ -4220,7 +4223,7 @@
       </c>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>158</v>
       </c>
@@ -4235,7 +4238,7 @@
       </c>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>158</v>
       </c>
@@ -4250,7 +4253,7 @@
       </c>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>158</v>
       </c>
@@ -4265,7 +4268,7 @@
       </c>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>158</v>
       </c>
@@ -4280,7 +4283,7 @@
       </c>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>158</v>
       </c>
@@ -4295,7 +4298,7 @@
       </c>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>158</v>
       </c>
@@ -4310,7 +4313,7 @@
       </c>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>158</v>
       </c>
@@ -4325,7 +4328,7 @@
       </c>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>158</v>
       </c>
@@ -4340,7 +4343,7 @@
       </c>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>158</v>
       </c>
@@ -4355,7 +4358,7 @@
       </c>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>158</v>
       </c>
@@ -4370,7 +4373,7 @@
       </c>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>158</v>
       </c>
@@ -4385,7 +4388,7 @@
       </c>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>158</v>
       </c>
@@ -4400,7 +4403,7 @@
       </c>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>158</v>
       </c>
@@ -4415,7 +4418,7 @@
       </c>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>158</v>
       </c>
@@ -4430,7 +4433,7 @@
       </c>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>158</v>
       </c>
@@ -4445,7 +4448,7 @@
       </c>
       <c r="E208" s="3"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>158</v>
       </c>
@@ -4460,7 +4463,7 @@
       </c>
       <c r="E209" s="3"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>158</v>
       </c>
@@ -4475,7 +4478,7 @@
       </c>
       <c r="E210" s="3"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>158</v>
       </c>
@@ -4490,7 +4493,7 @@
       </c>
       <c r="E211" s="3"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>158</v>
       </c>
@@ -4505,7 +4508,7 @@
       </c>
       <c r="E212" s="3"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>158</v>
       </c>
@@ -4520,7 +4523,7 @@
       </c>
       <c r="E213" s="3"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>158</v>
       </c>
@@ -4535,7 +4538,7 @@
       </c>
       <c r="E214" s="3"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>158</v>
       </c>
@@ -4550,7 +4553,7 @@
       </c>
       <c r="E215" s="3"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>158</v>
       </c>
@@ -4565,7 +4568,7 @@
       </c>
       <c r="E216" s="3"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>158</v>
       </c>
@@ -4580,7 +4583,7 @@
       </c>
       <c r="E217" s="3"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>158</v>
       </c>
@@ -4595,7 +4598,7 @@
       </c>
       <c r="E218" s="3"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>158</v>
       </c>
@@ -4610,7 +4613,7 @@
       </c>
       <c r="E219" s="3"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>158</v>
       </c>
@@ -4626,15 +4629,15 @@
       <c r="E220" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E220" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4674,7 +4677,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -4685,7 +4688,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -4961,7 +4964,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:C29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Java_Developer_Roadmap.xlsx
+++ b/Java_Developer_Roadmap.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21781D15-31A8-4F80-B52B-91344B343FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Roadmap" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Topics &amp; Subtopics" state="visible" r:id="rId5"/>
+    <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
+    <sheet name="Topics &amp; Subtopics" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Topics &amp; Subtopics'!$A$1:$C$29</definedName>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="289">
   <si>
     <t>Level</t>
   </si>
@@ -882,24 +883,27 @@
   </si>
   <si>
     <t>Images/containers; Dockerfile; commands; ports; environment; Compose; Spring Boot + DB</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1245,9 +1249,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E220"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F220"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1256,7 +1260,7 @@
     <col min="5" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +1277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1289,8 +1293,11 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1306,8 +1313,11 @@
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1323,8 +1333,11 @@
       <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -1340,8 +1353,11 @@
       <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1357,8 +1373,11 @@
       <c r="E6" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1374,8 +1393,11 @@
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1391,8 +1413,11 @@
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1408,8 +1433,11 @@
       <c r="E9" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1425,8 +1453,11 @@
       <c r="E10" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -1442,8 +1473,11 @@
       <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1459,8 +1493,11 @@
       <c r="E12" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -1476,8 +1513,11 @@
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -1494,7 +1534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -1511,7 +1551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -1943,7 +1983,7 @@
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
@@ -1958,7 +1998,7 @@
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>26</v>
       </c>
@@ -1973,7 +2013,7 @@
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>26</v>
       </c>
@@ -1988,7 +2028,7 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>26</v>
       </c>
@@ -2003,7 +2043,7 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>26</v>
       </c>
@@ -2018,7 +2058,7 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>26</v>
       </c>
@@ -2033,7 +2073,7 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>26</v>
       </c>
@@ -2048,7 +2088,7 @@
       </c>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
@@ -2063,7 +2103,7 @@
       </c>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>61</v>
       </c>
@@ -2078,7 +2118,7 @@
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>61</v>
       </c>
@@ -2093,7 +2133,7 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>61</v>
       </c>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>61</v>
       </c>
@@ -2123,7 +2163,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>61</v>
       </c>
@@ -2138,7 +2178,7 @@
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>61</v>
       </c>
@@ -2153,7 +2193,7 @@
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
@@ -2168,7 +2208,7 @@
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
@@ -2183,7 +2223,7 @@
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>61</v>
       </c>
@@ -2198,7 +2238,7 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -2213,7 +2253,7 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>61</v>
       </c>
@@ -2228,7 +2268,7 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
@@ -2243,7 +2283,7 @@
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>61</v>
       </c>
@@ -2258,7 +2298,7 @@
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
@@ -2273,7 +2313,7 @@
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>61</v>
       </c>
@@ -2288,7 +2328,7 @@
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>61</v>
       </c>
@@ -2303,7 +2343,7 @@
       </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>61</v>
       </c>
@@ -2318,7 +2358,7 @@
       </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>61</v>
       </c>
@@ -2333,7 +2373,7 @@
       </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>61</v>
       </c>
@@ -2348,7 +2388,7 @@
       </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>61</v>
       </c>
@@ -2363,7 +2403,7 @@
       </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>61</v>
       </c>
@@ -2378,7 +2418,7 @@
       </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>61</v>
       </c>
@@ -2393,7 +2433,7 @@
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>61</v>
       </c>
@@ -2408,7 +2448,7 @@
       </c>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>61</v>
       </c>
@@ -2423,7 +2463,7 @@
       </c>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>61</v>
       </c>
@@ -2438,7 +2478,7 @@
       </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>61</v>
       </c>
@@ -2453,7 +2493,7 @@
       </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>61</v>
       </c>
@@ -2468,7 +2508,7 @@
       </c>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>61</v>
       </c>
@@ -2483,7 +2523,7 @@
       </c>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -2498,7 +2538,7 @@
       </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>61</v>
       </c>
@@ -2513,7 +2553,7 @@
       </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>61</v>
       </c>
@@ -2528,7 +2568,7 @@
       </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>61</v>
       </c>
@@ -2543,7 +2583,7 @@
       </c>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>61</v>
       </c>
@@ -2558,7 +2598,7 @@
       </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>61</v>
       </c>
@@ -2573,7 +2613,7 @@
       </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>61</v>
       </c>
@@ -2588,7 +2628,7 @@
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
@@ -2603,7 +2643,7 @@
       </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>61</v>
       </c>
@@ -2618,7 +2658,7 @@
       </c>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>61</v>
       </c>
@@ -2633,7 +2673,7 @@
       </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
@@ -2648,7 +2688,7 @@
       </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>61</v>
       </c>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>61</v>
       </c>
@@ -2678,7 +2718,7 @@
       </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>61</v>
       </c>
@@ -2693,7 +2733,7 @@
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>61</v>
       </c>
@@ -2708,7 +2748,7 @@
       </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>61</v>
       </c>
@@ -2723,7 +2763,7 @@
       </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>61</v>
       </c>
@@ -2738,7 +2778,7 @@
       </c>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>61</v>
       </c>
@@ -2753,7 +2793,7 @@
       </c>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>61</v>
       </c>
@@ -2768,7 +2808,7 @@
       </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>61</v>
       </c>
@@ -2783,7 +2823,7 @@
       </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>61</v>
       </c>
@@ -2798,7 +2838,7 @@
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>61</v>
       </c>
@@ -2813,7 +2853,7 @@
       </c>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>61</v>
       </c>
@@ -2828,7 +2868,7 @@
       </c>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>120</v>
       </c>
@@ -2843,7 +2883,7 @@
       </c>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>120</v>
       </c>
@@ -2858,7 +2898,7 @@
       </c>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>120</v>
       </c>
@@ -2873,7 +2913,7 @@
       </c>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
@@ -2888,7 +2928,7 @@
       </c>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>120</v>
       </c>
@@ -2903,7 +2943,7 @@
       </c>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>120</v>
       </c>
@@ -2918,7 +2958,7 @@
       </c>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>120</v>
       </c>
@@ -2933,7 +2973,7 @@
       </c>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>120</v>
       </c>
@@ -2948,7 +2988,7 @@
       </c>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>120</v>
       </c>
@@ -2963,7 +3003,7 @@
       </c>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>120</v>
       </c>
@@ -2978,7 +3018,7 @@
       </c>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>120</v>
       </c>
@@ -2993,7 +3033,7 @@
       </c>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>120</v>
       </c>
@@ -3008,7 +3048,7 @@
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>120</v>
       </c>
@@ -3023,7 +3063,7 @@
       </c>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>120</v>
       </c>
@@ -3038,7 +3078,7 @@
       </c>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>120</v>
       </c>
@@ -3053,7 +3093,7 @@
       </c>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>120</v>
       </c>
@@ -3068,7 +3108,7 @@
       </c>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>120</v>
       </c>
@@ -3083,7 +3123,7 @@
       </c>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>120</v>
       </c>
@@ -3098,7 +3138,7 @@
       </c>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>120</v>
       </c>
@@ -3113,7 +3153,7 @@
       </c>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>120</v>
       </c>
@@ -3128,7 +3168,7 @@
       </c>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>120</v>
       </c>
@@ -3143,7 +3183,7 @@
       </c>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
@@ -3158,7 +3198,7 @@
       </c>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>120</v>
       </c>
@@ -3173,7 +3213,7 @@
       </c>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>120</v>
       </c>
@@ -3188,7 +3228,7 @@
       </c>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -3203,7 +3243,7 @@
       </c>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
@@ -3218,7 +3258,7 @@
       </c>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>120</v>
       </c>
@@ -3233,7 +3273,7 @@
       </c>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>120</v>
       </c>
@@ -3248,7 +3288,7 @@
       </c>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>120</v>
       </c>
@@ -3263,7 +3303,7 @@
       </c>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>120</v>
       </c>
@@ -3278,7 +3318,7 @@
       </c>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>120</v>
       </c>
@@ -3293,7 +3333,7 @@
       </c>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>120</v>
       </c>
@@ -3308,7 +3348,7 @@
       </c>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>158</v>
       </c>
@@ -3323,7 +3363,7 @@
       </c>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>158</v>
       </c>
@@ -3338,7 +3378,7 @@
       </c>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>158</v>
       </c>
@@ -3353,7 +3393,7 @@
       </c>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>158</v>
       </c>
@@ -3368,7 +3408,7 @@
       </c>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>158</v>
       </c>
@@ -3383,7 +3423,7 @@
       </c>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>158</v>
       </c>
@@ -3398,7 +3438,7 @@
       </c>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>158</v>
       </c>
@@ -3413,7 +3453,7 @@
       </c>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>158</v>
       </c>
@@ -3428,7 +3468,7 @@
       </c>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>158</v>
       </c>
@@ -3443,7 +3483,7 @@
       </c>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>158</v>
       </c>
@@ -3458,7 +3498,7 @@
       </c>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>158</v>
       </c>
@@ -3473,7 +3513,7 @@
       </c>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>158</v>
       </c>
@@ -3488,7 +3528,7 @@
       </c>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>158</v>
       </c>
@@ -3503,7 +3543,7 @@
       </c>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>158</v>
       </c>
@@ -3518,7 +3558,7 @@
       </c>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>158</v>
       </c>
@@ -3533,7 +3573,7 @@
       </c>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
@@ -3548,7 +3588,7 @@
       </c>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>158</v>
       </c>
@@ -3563,7 +3603,7 @@
       </c>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>158</v>
       </c>
@@ -3578,7 +3618,7 @@
       </c>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>158</v>
       </c>
@@ -3593,7 +3633,7 @@
       </c>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>158</v>
       </c>
@@ -3608,7 +3648,7 @@
       </c>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>158</v>
       </c>
@@ -3623,7 +3663,7 @@
       </c>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>158</v>
       </c>
@@ -3638,7 +3678,7 @@
       </c>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>158</v>
       </c>
@@ -3653,7 +3693,7 @@
       </c>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
@@ -3668,7 +3708,7 @@
       </c>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>158</v>
       </c>
@@ -3683,7 +3723,7 @@
       </c>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>158</v>
       </c>
@@ -3698,7 +3738,7 @@
       </c>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>158</v>
       </c>
@@ -3713,7 +3753,7 @@
       </c>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>158</v>
       </c>
@@ -3728,7 +3768,7 @@
       </c>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>158</v>
       </c>
@@ -3743,7 +3783,7 @@
       </c>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>158</v>
       </c>
@@ -3758,7 +3798,7 @@
       </c>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>158</v>
       </c>
@@ -3773,7 +3813,7 @@
       </c>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>158</v>
       </c>
@@ -3788,7 +3828,7 @@
       </c>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>158</v>
       </c>
@@ -3803,7 +3843,7 @@
       </c>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>158</v>
       </c>
@@ -3818,7 +3858,7 @@
       </c>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -3833,7 +3873,7 @@
       </c>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>158</v>
       </c>
@@ -3848,7 +3888,7 @@
       </c>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>158</v>
       </c>
@@ -3863,7 +3903,7 @@
       </c>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>158</v>
       </c>
@@ -3878,7 +3918,7 @@
       </c>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>158</v>
       </c>
@@ -3893,7 +3933,7 @@
       </c>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>158</v>
       </c>
@@ -3908,7 +3948,7 @@
       </c>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>158</v>
       </c>
@@ -3923,7 +3963,7 @@
       </c>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>158</v>
       </c>
@@ -3938,7 +3978,7 @@
       </c>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>158</v>
       </c>
@@ -3953,7 +3993,7 @@
       </c>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>158</v>
       </c>
@@ -3968,7 +4008,7 @@
       </c>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>158</v>
       </c>
@@ -3983,7 +4023,7 @@
       </c>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>158</v>
       </c>
@@ -3998,7 +4038,7 @@
       </c>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>158</v>
       </c>
@@ -4013,7 +4053,7 @@
       </c>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>158</v>
       </c>
@@ -4028,7 +4068,7 @@
       </c>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>158</v>
       </c>
@@ -4043,7 +4083,7 @@
       </c>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>158</v>
       </c>
@@ -4058,7 +4098,7 @@
       </c>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>158</v>
       </c>
@@ -4073,7 +4113,7 @@
       </c>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>158</v>
       </c>
@@ -4088,7 +4128,7 @@
       </c>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>158</v>
       </c>
@@ -4103,7 +4143,7 @@
       </c>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>158</v>
       </c>
@@ -4118,7 +4158,7 @@
       </c>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>158</v>
       </c>
@@ -4133,7 +4173,7 @@
       </c>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>158</v>
       </c>
@@ -4148,7 +4188,7 @@
       </c>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>158</v>
       </c>
@@ -4163,7 +4203,7 @@
       </c>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>158</v>
       </c>
@@ -4178,7 +4218,7 @@
       </c>
       <c r="E190" s="3"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>158</v>
       </c>
@@ -4193,7 +4233,7 @@
       </c>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>158</v>
       </c>
@@ -4208,7 +4248,7 @@
       </c>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>158</v>
       </c>
@@ -4223,7 +4263,7 @@
       </c>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>158</v>
       </c>
@@ -4238,7 +4278,7 @@
       </c>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>158</v>
       </c>
@@ -4253,7 +4293,7 @@
       </c>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>158</v>
       </c>
@@ -4268,7 +4308,7 @@
       </c>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>158</v>
       </c>
@@ -4283,7 +4323,7 @@
       </c>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>158</v>
       </c>
@@ -4298,7 +4338,7 @@
       </c>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>158</v>
       </c>
@@ -4313,7 +4353,7 @@
       </c>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>158</v>
       </c>
@@ -4328,7 +4368,7 @@
       </c>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>158</v>
       </c>
@@ -4343,7 +4383,7 @@
       </c>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>158</v>
       </c>
@@ -4358,7 +4398,7 @@
       </c>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>158</v>
       </c>
@@ -4373,7 +4413,7 @@
       </c>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>158</v>
       </c>
@@ -4388,7 +4428,7 @@
       </c>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>158</v>
       </c>
@@ -4403,7 +4443,7 @@
       </c>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>158</v>
       </c>
@@ -4418,7 +4458,7 @@
       </c>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>158</v>
       </c>
@@ -4433,7 +4473,7 @@
       </c>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>158</v>
       </c>
@@ -4448,7 +4488,7 @@
       </c>
       <c r="E208" s="3"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>158</v>
       </c>
@@ -4463,7 +4503,7 @@
       </c>
       <c r="E209" s="3"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>158</v>
       </c>
@@ -4478,7 +4518,7 @@
       </c>
       <c r="E210" s="3"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>158</v>
       </c>
@@ -4493,7 +4533,7 @@
       </c>
       <c r="E211" s="3"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>158</v>
       </c>
@@ -4508,7 +4548,7 @@
       </c>
       <c r="E212" s="3"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>158</v>
       </c>
@@ -4523,7 +4563,7 @@
       </c>
       <c r="E213" s="3"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>158</v>
       </c>
@@ -4538,7 +4578,7 @@
       </c>
       <c r="E214" s="3"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>158</v>
       </c>
@@ -4553,7 +4593,7 @@
       </c>
       <c r="E215" s="3"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>158</v>
       </c>
@@ -4568,7 +4608,7 @@
       </c>
       <c r="E216" s="3"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>158</v>
       </c>
@@ -4583,7 +4623,7 @@
       </c>
       <c r="E217" s="3"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>158</v>
       </c>
@@ -4598,7 +4638,7 @@
       </c>
       <c r="E218" s="3"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>158</v>
       </c>
@@ -4613,7 +4653,7 @@
       </c>
       <c r="E219" s="3"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>158</v>
       </c>
@@ -4629,15 +4669,15 @@
       <c r="E220" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E220"/>
+  <autoFilter ref="A1:E220" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4677,7 +4717,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -4688,7 +4728,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -4964,7 +5004,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C29"/>
+  <autoFilter ref="A1:C29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>